--- a/src/plugin-tables/behavior-plugin-tables-v0.8.xlsx
+++ b/src/plugin-tables/behavior-plugin-tables-v0.8.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>本工作簿专用于行为插件（可嵌入的攻击卡）设计，供设计 / 开发逐槽对照。赋能 / 中继插件另开工作簿。</t>
+          <t>本工作簿专用于行为插件（可嵌入的攻击插件）设计，供设计 / 开发逐槽对照。赋能 / 中继插件另开工作簿。</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>稀有度是插件的固有属性（一张卡固定一个稀有度档，不随槽位改变），同一插件以 I / II / III 三档存在。主表按每稀有度版本一行列出；B / C / D 分页给出三档实际数据。稀有度差异体现为 伤害成长系数（I ×1.0 / II ×1.2 / III ×1.4）+ 载荷档 + 偶发状态 / 控制差异；动作、热能、判定保持一致。当前从稀有度 I 开始设计。</t>
+          <t>稀有度是插件的固有属性（一个插件固定一个稀有度档，不随槽位改变），同一插件以 I / II / III 三档存在。主表按每稀有度版本一行列出；B / C / D 分页给出三档实际数据。稀有度差异体现为 伤害成长系数（I ×1.0 / II ×1.2 / III ×1.4）+ 载荷档 + 偶发状态 / 控制差异；动作、热能、判定保持一致。当前从稀有度 I 开始设计。</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>超限释放为单卡终结技，热能消耗需明显高于普攻 / 重装，并因插件不同而差异化（基本 &gt;60，热能上限120）：炽燃斩 65 / 涡刃绞击 75 / 重力轰拳 70。</t>
+          <t>超限释放为单插件终结技，热能消耗需明显高于普攻 / 重装，并因插件不同而差异化（基本 &gt;60，热能上限120）：炽燃斩 65 / 涡刃绞击 75 / 重力轰拳 70。</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>插件固有属性，分 I / II / III（传说另列）；一张卡固定一个稀有度档，不随槽位改变</t>
+          <t>插件固有属性，分 I / II / III（传说另列）；一个插件固定一个稀有度档，不随槽位改变</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2972,7 +2972,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>C. 重装序列（根卡 CD 特殊攻击）</t>
+          <t>C. 重装序列（根行为插件 CD 特殊攻击）</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>D. 超限释放（单卡终结技）</t>
+          <t>D. 超限释放（单插件终结技）</t>
         </is>
       </c>
     </row>

--- a/src/plugin-tables/behavior-plugin-tables-v0.8.xlsx
+++ b/src/plugin-tables/behavior-plugin-tables-v0.8.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -680,6 +680,18 @@
       <c r="B22" t="inlineStr">
         <is>
           <t>B / C / D『打击感反馈』列给出每槽命中反馈设计意图，按槽位节奏分级：攻击序列高频轻反馈、重装中频中反馈、超限低频强反馈。通用原则：普通怪受击即僵直；击退 / 牵引按数值向量处理（负值=吸入），支持环境击杀正反馈；蓄力型技能以蓄力暴露换范围；超限释放自带短暂保护帧防打断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>补入 9 个近战插件：雷矢链刺（感电）/ 侵蚀爪刃（侵蚀）/ 索锚打击（牵引）/ 爆震跃击 / 筑垒推进 / 蓄力重斩 / 多重连刺 / 破韧重装 / 铭痕裂击（标记联动）。主表 6→15 插件、18→45 行，三槽 × 三档全部落表。铭痕裂击只对「已标记敌人」增伤并延长标记，不施加、不引爆标记——标记的施加与引爆仍归赋能体系。</t>
         </is>
       </c>
     </row>
@@ -839,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1776,6 +1788,1302 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 感电</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_SLASH_I</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_BURST_I</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 感电</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>×1.2</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_SLASH_II</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_BURST_II</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 感电</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>×1.4</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_SLASH_III</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_BURST_III</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 侵蚀</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_SLASH_I</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_BURST_I</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 侵蚀</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>×1.2</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_SLASH_II</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_BURST_II</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 侵蚀</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>×1.4</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_SLASH_III</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_BURST_III</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 牵引</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_SLASH_I</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_BURST_I</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 牵引</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>×1.2</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_SLASH_II</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_BURST_II</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 牵引</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>×1.4</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_SLASH_III</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_BURST_III</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_SLASH_I</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_BURST_I</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>×1.2</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_SLASH_II</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_BURST_II</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>×1.4</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_SLASH_III</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_BURST_III</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_SLASH_I</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_BURST_I</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>×1.2</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_SLASH_II</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_BURST_II</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>×1.4</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_SLASH_III</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_BURST_III</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_SLASH_I</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_BURST_I</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>×1.2</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_SLASH_II</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_BURST_II</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>×1.4</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_SLASH_III</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_BURST_III</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_SLASH_I</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_BURST_I</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>×1.2</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_SLASH_II</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_BURST_II</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>×1.4</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_SLASH_III</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_BURST_III</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_SLASH_I</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_BURST_I</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>×1.2</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_SLASH_II</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_BURST_II</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>×1.4</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_SLASH_III</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_BURST_III</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 标记联动</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_SLASH_I</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_BURST_I</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 标记联动</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>×1.2</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_SLASH_II</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_BURST_II</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>近战 / 标记联动</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>×1.4</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_SLASH_III</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_BURST_III</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>近战池补全（2026-10-27）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1787,7 +3095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2941,6 +4249,1626 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_SLASH_I</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺 I·攻</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>三段高频链刺：电步突刺 / 回身斜刺 / 引雷回拉；每段命中后向最近敌人弹射一次电弧</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>3+4+5（每段弹射 +2）</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>三段短距电步突刺：第1段正面窄扇形 / 第2段斜向窄扇形 / 第3段回身刺；每段命中后自动向最近敌人弹射 1 次（同目标不重复，弹射伤害为该段 60%），每跳短僵直</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>每段命中累计感电值（起手/连段轻积累）；弹射跳累计少量</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 链式弹射铺感电 · 每跳僵直（硬直非麻痹）；感电不叠层</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>电步残影+电流噼啪；每跳命中短僵直+电弧尾迹，弹射链拉出一串电火花</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_SLASH_II</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺 II·攻</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>三段高频链刺：电步突刺 / 回身斜刺 / 引雷回拉；每段命中后向最近敌人弹射一次电弧</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>4+5+6（每段弹射 +2）</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>三段短距电步突刺：第1段正面窄扇形 / 第2段斜向窄扇形 / 第3段回身刺；每段命中后自动向最近敌人弹射 1 次（同目标不重复，弹射伤害为该段 60%），每跳短僵直</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>每段命中累计感电值（起手/连段轻积累）；弹射跳累计少量</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 链式弹射铺感电 · 每跳僵直（硬直非麻痹）；感电不叠层</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>电步残影+电流噼啪；每跳命中短僵直+电弧尾迹，弹射链拉出一串电火花</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_SLASH_III</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺 III·攻</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>三段高频链刺：电步突刺 / 回身斜刺 / 引雷回拉；每段命中后向最近敌人弹射一次电弧</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>4+6+7（每段弹射 +3）</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>三段短距电步突刺：第1段正面窄扇形 / 第2段斜向窄扇形 / 第3段回身刺；每段命中后自动向最近敌人弹射 1 次（同目标不重复，弹射伤害为该段 60%），每跳短僵直</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>每段命中累计感电值（起手/连段轻积累）；弹射跳累计少量</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 链式弹射铺感电 · 每跳僵直（硬直非麻痹）；感电不叠层</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>电步残影+电流噼啪；每跳命中短僵直+电弧尾迹，弹射链拉出一串电火花</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_SLASH_I</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃 I·攻</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>三段高速爪击：左爪横扫 / 右爪斜撕 / 双爪交叉撕裂</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>4+5+6</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>三段短步爪击：第1段正面小扇形 / 第2段斜向窄扇形 / 第3段双爪交叉大扇形；命中附腐化减速（移速 -20%，1.5s，非状态）</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>每段命中累计侵蚀值（起手/连段轻积累）</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 高速爪击铺层 · 附腐化减速（非状态）</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>爪光拖酸蚀尾迹；高频撕裂金属声，每段轻顿帧+酸蚀烟点，末段交叉撕开大硬直</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_SLASH_II</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃 II·攻</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>三段高速爪击：左爪横扫 / 右爪斜撕 / 双爪交叉撕裂</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>5+6+7</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>三段短步爪击：第1段正面小扇形 / 第2段斜向窄扇形 / 第3段双爪交叉大扇形；命中附腐化减速（移速 -20%，1.5s，非状态）</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>每段命中累计侵蚀值（起手/连段轻积累）</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 高速爪击铺层 · 附腐化减速（非状态）</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>爪光拖酸蚀尾迹；高频撕裂金属声，每段轻顿帧+酸蚀烟点，末段交叉撕开大硬直</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_SLASH_III</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃 III·攻</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>三段高速爪击：左爪横扫 / 右爪斜撕 / 双爪交叉撕裂</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>6+7+8</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>三段短步爪击：第1段正面小扇形 / 第2段斜向窄扇形 / 第3段双爪交叉大扇形；命中附腐化减速（移速 -20%，1.5s，非状态）</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>每段命中累计侵蚀值（起手/连段轻积累）</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 高速爪击铺层 · 附腐化减速（非状态）</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>爪光拖酸蚀尾迹；高频撕裂金属声，每段轻顿帧+酸蚀烟点，末段交叉撕开大硬直</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_SLASH_I</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击 I·攻</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>掷出锚钩勾住首个敌人，猛地拉至面前，接一记钉刺</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>4+6+7</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>掷锚直线命中首个敌人：拉近过程中造成伤害，拉到面前后追加钉刺；拉近后定身 1s；对精英/Boss 拉近距离减半（不免疫）</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>无（控制类，非状态）</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 钩索拉近聚怪 · 定身钉住</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>锚链绷紧的金属摩擦声；拉近拖拽感强，钉刺落地重顿帧+尘环</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_SLASH_II</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击 II·攻</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>掷出锚钩勾住首个敌人，猛地拉至面前，接一记钉刺</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>5+7+8</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>掷锚直线命中首个敌人：拉近过程中造成伤害，拉到面前后追加钉刺；拉近后定身 1s；对精英/Boss 拉近距离减半（不免疫）</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>无（控制类，非状态）</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 钩索拉近聚怪 · 定身钉住</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>锚链绷紧的金属摩擦声；拉近拖拽感强，钉刺落地重顿帧+尘环</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_SLASH_III</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击 III·攻</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>掷出锚钩勾住首个敌人，猛地拉至面前，接一记钉刺</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>6+8+10</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>掷锚直线命中首个敌人：拉近过程中造成伤害，拉到面前后追加钉刺；拉近后定身 1s；对精英/Boss 拉近距离减半（不免疫）</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>无（控制类，非状态）</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 钩索拉近聚怪 · 定身钉住</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>锚链绷紧的金属摩擦声；拉近拖拽感强，钉刺落地重顿帧+尘环</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_SLASH_I</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击 I·攻</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>短距前跃，落地砸击掀起小范围冲击波</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>5+7+8</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>短距前跳（跃起 0.2s 无敌帧），落地砸击 + 小范围冲击波；中心全额、边缘 60%</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 短跃 · 落地小震</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>跃起镜头轻抬；落地小震屏+尘环扩散，冲击波扫过敌人轻硬直</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_SLASH_II</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击 II·攻</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>短距前跃，落地砸击掀起小范围冲击波</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>6+8+10</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>短距前跳（跃起 0.2s 无敌帧），落地砸击 + 小范围冲击波；中心全额、边缘 60%</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 短跃 · 落地小震</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>跃起镜头轻抬；落地小震屏+尘环扩散，冲击波扫过敌人轻硬直</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_SLASH_III</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击 III·攻</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>短距前跃，落地砸击掀起小范围冲击波</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>7+10+11</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>短距前跳（跃起 0.2s 无敌帧），落地砸击 + 小范围冲击波；中心全额、边缘 60%</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 短跃 · 落地小震</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>跃起镜头轻抬；落地小震屏+尘环扩散，冲击波扫过敌人轻硬直</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_SLASH_I</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进 I·攻</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>举盾前推，盾面连续顶撞，正面弹幕被弹开</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>4+5+6</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>举盾慢推（移速 -50%），正面小扇形盾击；推进中正面弹幕被盾面反弹（反射 50% 伤害回射）</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 举盾慢推 · 正面弹幕反弹</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>盾面金属摩擦声；弹幕被弹开的火花四溅，盾击闷响+轻震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_SLASH_II</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进 II·攻</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>举盾前推，盾面连续顶撞，正面弹幕被弹开</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>5+6+7</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>举盾慢推（移速 -50%），正面小扇形盾击；推进中正面弹幕被盾面反弹（反射 50% 伤害回射）</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 举盾慢推 · 正面弹幕反弹</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>盾面金属摩擦声；弹幕被弹开的火花四溅，盾击闷响+轻震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_SLASH_III</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进 III·攻</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>举盾前推，盾面连续顶撞，正面弹幕被弹开</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>6+7+8</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>举盾慢推（移速 -50%），正面小扇形盾击；推进中正面弹幕被盾面反弹（反射 50% 伤害回射）</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 举盾慢推 · 正面弹幕反弹</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>盾面金属摩擦声；弹幕被弹开的火花四溅，盾击闷响+轻震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_SLASH_I</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩 I·攻</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>点按轻斩；长按蓄力，松手释放宽扇形重斩</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>点按 5；蓄力 0.5s 9 / 1.0s 13 / 1.5s 17（满蓄）</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>点按 2；蓄力每 0.5s +2（最高 +6）</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>点按窄扇形轻斩；长按蓄力（移速 -30%），1.5s 满蓄，松手释放宽扇形斩；满蓄命中附强击退</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 蓄力宽斩 · 满蓄强击退</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>蓄力刃光渐亮、低频蓄能音；满蓄释放大顿帧+强击退，刀风撕开地面尘线</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_SLASH_II</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩 II·攻</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>点按轻斩；长按蓄力，松手释放宽扇形重斩</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>点按 6；蓄力 0.5s 11 / 1.0s 16 / 1.5s 20</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>点按 2；蓄力每 0.5s +2（最高 +6）</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>点按窄扇形轻斩；长按蓄力（移速 -30%），1.5s 满蓄，松手释放宽扇形斩；满蓄命中附强击退</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 蓄力宽斩 · 满蓄强击退</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>蓄力刃光渐亮、低频蓄能音；满蓄释放大顿帧+强击退，刀风撕开地面尘线</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_SLASH_III</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩 III·攻</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>点按轻斩；长按蓄力，松手释放宽扇形重斩</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>点按 7；蓄力 0.5s 13 / 1.0s 18 / 1.5s 24</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>点按 2；蓄力每 0.5s +2（最高 +6）</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>点按窄扇形轻斩；长按蓄力（移速 -30%），1.5s 满蓄，松手释放宽扇形斩；满蓄命中附强击退</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 蓄力宽斩 · 满蓄强击退</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>蓄力刃光渐亮、低频蓄能音；满蓄释放大顿帧+强击退，刀风撕开地面尘线</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_SLASH_I</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺 I·攻</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>五段高速连刺，每段短距滑步跟进</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>2+3+3+4+5</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>每段 2（共 5 段）</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>五段高速突刺，每段短距滑步跟进（位移滑步）；末段轻推</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 五段连刺 · 滑步跟进</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>密集刺击金属声；每段轻顿帧+火花，末段轻推</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_SLASH_II</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺 II·攻</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>五段高速连刺，每段短距滑步跟进</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4+5+6</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>每段 2（共 5 段）</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>五段高速突刺，每段短距滑步跟进（位移滑步）；末段轻推</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 五段连刺 · 滑步跟进</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>密集刺击金属声；每段轻顿帧+火花，末段轻推</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_SLASH_III</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺 III·攻</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>五段高速连刺，每段短距滑步跟进</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>3+4+5+6+7</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>每段 2（共 5 段）</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>五段高速突刺，每段短距滑步跟进（位移滑步）；末段轻推</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 五段连刺 · 滑步跟进</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>密集刺击金属声；每段轻顿帧+火花，末段轻推</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_SLASH_I</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装 I·攻</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>三段重锤砸地，每段附高削韧</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>6+8+10</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>三段重砸：第1段正面小范围 / 第2段窄范围 / 第3段大范围砸地；每段附高削韧量</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 三段重砸 · 高削韧</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>重锤砸地厚重顿帧；地面裂纹逐段扩散，末段大震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_SLASH_II</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装 II·攻</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>三段重锤砸地，每段附高削韧</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>7+10+12</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>三段重砸：第1段正面小范围 / 第2段窄范围 / 第3段大范围砸地；每段附高削韧量</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 三段重砸 · 高削韧</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>重锤砸地厚重顿帧；地面裂纹逐段扩散，末段大震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_SLASH_III</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装 III·攻</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>三段重锤砸地，每段附高削韧</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>8+11+14</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>三段重砸：第1段正面小范围 / 第2段窄范围 / 第3段大范围砸地；每段附高削韧量</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 三段重砸 · 高削韧</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>重锤砸地厚重顿帧；地面裂纹逐段扩散，末段大震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_SLASH_I</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击 I·攻</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>三段斩击，命中已标记敌人时附加额外伤害并延长标记</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>4+6+8</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>三段斩击（正面小扇形 / 窄扇形 / 大扇形）；命中已标记敌人时每段附加 3 点固定伤害并延长标记 0.5s（不消耗标记）</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>无（不施加、不引爆标记；仅对已标记敌人增伤）</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 标记联动 · 命中已标记敌加伤（行为插件不施加/不引爆标记）</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>斩击划过标记裂纹，裂纹光爆闪；附加伤害为独立白色数字</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_SLASH_II</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击 II·攻</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>三段斩击，命中已标记敌人时附加额外伤害并延长标记</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>5+7+10</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>三段斩击（正面小扇形 / 窄扇形 / 大扇形）；命中已标记敌人时每段附加 3 点固定伤害并延长标记 0.5s（不消耗标记）</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>无（不施加、不引爆标记；仅对已标记敌人增伤）</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 标记联动 · 命中已标记敌加伤（行为插件不施加/不引爆标记）</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>斩击划过标记裂纹，裂纹光爆闪；附加伤害为独立白色数字</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_SLASH_III</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击 III·攻</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>三段斩击，命中已标记敌人时附加额外伤害并延长标记</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>6+9+11</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>2+3+4</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>三段斩击（正面小扇形 / 窄扇形 / 大扇形）；命中已标记敌人时每段附加 3 点固定伤害并延长标记 0.5s（不消耗标记）</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>无（不施加、不引爆标记；仅对已标记敌人增伤）</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 标记联动 · 命中已标记敌加伤（行为插件不施加/不引爆标记）</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>斩击划过标记裂纹，裂纹光爆闪；附加伤害为独立白色数字</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2952,7 +5880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4082,6 +7010,1626 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_BURST_I</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺 I·装</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>中距电步突进，刺穿首个目标后向周围 3 个敌人弹射电弧</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>18 + 弹射 6×3</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>中距直线电步突进（路径命中短僵直）；命中点向周围 3 个敌人各弹射 1 道电弧（伤害为该次命中的 35%）</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>命中累计中等感电值；弹射跳累计少量</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 突进+三向弹射 · 硬直非麻痹；弹射数不随稀有度增加，只递进伤害</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>电步拖出电流残影；突进雷爆中顿帧，三向电弧炸开，命中目标硬直定格</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_BURST_II</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺 II·装</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>中距电步突进，刺穿首个目标后向周围 3 个敌人弹射电弧</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>22 + 弹射 7×3</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>中距直线电步突进（路径命中短僵直）；命中点向周围 3 个敌人各弹射 1 道电弧（伤害为该次命中的 35%）</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>命中累计中等感电值；弹射跳累计少量</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 突进+三向弹射 · 硬直非麻痹；弹射数不随稀有度增加，只递进伤害</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>电步拖出电流残影；突进雷爆中顿帧，三向电弧炸开，命中目标硬直定格</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_BURST_III</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺 III·装</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>中距电步突进，刺穿首个目标后向周围 3 个敌人弹射电弧</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>25 + 弹射 9×3</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>中距直线电步突进（路径命中短僵直）；命中点向周围 3 个敌人各弹射 1 道电弧（伤害为该次命中的 35%）</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>命中累计中等感电值；弹射跳累计少量</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 突进+三向弹射 · 硬直非麻痹；弹射数不随稀有度增加，只递进伤害</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>电步拖出电流残影；突进雷爆中顿帧，三向电弧炸开，命中目标硬直定格</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_BURST_I</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃 I·装</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>中距爪光突进，路径留下腐蚀带</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>18+10+10</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>中距直线突进，命中撕裂；路径留下腐蚀带（3s，每 0.5s 结算一次，带内敌人移速 -30% 并累计少量侵蚀值）</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>命中累计中等侵蚀值；腐蚀带每 0.5s 累计少量侵蚀值</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 突进留腐蚀带 · 持续铺侵蚀</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>突进撕开酸雾；腐蚀带地面冒泡扩散，带内敌人持续受蚀、脚步拖滞</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_BURST_II</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃 II·装</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>中距爪光突进，路径留下腐蚀带</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>22+12+12</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>中距直线突进，命中撕裂；路径留下腐蚀带（3s，每 0.5s 结算一次，带内敌人移速 -30% 并累计少量侵蚀值）</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>命中累计中等侵蚀值；腐蚀带每 0.5s 累计少量侵蚀值</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 突进留腐蚀带 · 持续铺侵蚀</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>突进撕开酸雾；腐蚀带地面冒泡扩散，带内敌人持续受蚀、脚步拖滞</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_BURST_III</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃 III·装</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>中距爪光突进，路径留下腐蚀带</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>25+14+14</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>中距直线突进，命中撕裂；路径留下腐蚀带（3s，每 0.5s 结算一次，带内敌人移速 -30% 并累计少量侵蚀值）</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>命中累计中等侵蚀值；腐蚀带每 0.5s 累计少量侵蚀值</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 突进留腐蚀带 · 持续铺侵蚀</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>突进撕开酸雾；腐蚀带地面冒泡扩散，带内敌人持续受蚀、脚步拖滞</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_BURST_I</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击 I·装</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>反向钩索：掷锚钉住目标，借力把自己拽向敌人，落点钉刺</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>22+20</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>掷锚命中后自身被拉向目标（反向位移），落点钉刺；命中敌人定身 1.2s</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>无（控制类，非状态）</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 反向钩索突进 · 定身</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>锚链回拉带动镜头前冲；落点钉刺重震屏，被钉目标硬直定格</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_BURST_II</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击 II·装</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>反向钩索：掷锚钉住目标，借力把自己拽向敌人，落点钉刺</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>26+24</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>掷锚命中后自身被拉向目标（反向位移），落点钉刺；命中敌人定身 1.2s</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>无（控制类，非状态）</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 反向钩索突进 · 定身</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>锚链回拉带动镜头前冲；落点钉刺重震屏，被钉目标硬直定格</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_BURST_III</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击 III·装</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>反向钩索：掷锚钉住目标，借力把自己拽向敌人，落点钉刺</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>31+28</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>掷锚命中后自身被拉向目标（反向位移），落点钉刺；命中敌人定身 1.2s</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>无（控制类，非状态）</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 反向钩索突进 · 定身</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>锚链回拉带动镜头前冲；落点钉刺重震屏，被钉目标硬直定格</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_BURST_I</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击 I·装</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>高跳后重砸落地，掀起大范围冲击波</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>30+15</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>高跳（滞空 0.4s，可微调落点），落地砸出半径大冲击波；中心全额、边缘 60%</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 高跳砸地 · 大范围 AOE</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>滞空蓄势镜头拉远；落地大震屏+环形尘爆，边缘敌人被冲击波推倒</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_BURST_II</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击 II·装</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>高跳后重砸落地，掀起大范围冲击波</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>36+18</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>高跳（滞空 0.4s，可微调落点），落地砸出半径大冲击波；中心全额、边缘 60%</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 高跳砸地 · 大范围 AOE</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>滞空蓄势镜头拉远；落地大震屏+环形尘爆，边缘敌人被冲击波推倒</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_BURST_III</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击 III·装</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>高跳后重砸落地，掀起大范围冲击波</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>42+21</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>高跳（滞空 0.4s，可微调落点），落地砸出半径大冲击波；中心全额、边缘 60%</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 高跳砸地 · 大范围 AOE</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>滞空蓄势镜头拉远；落地大震屏+环形尘爆，边缘敌人被冲击波推倒</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_BURST_I</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进 I·装</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>举盾冲刺，撞开路径敌人并反弹沿途弹幕</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>18+14</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>中距盾冲，冲刺中正面弹幕全部反弹；末端盾击击退</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 冲刺反弹 · 击退（防御向，伤害低于同档输出型）</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>冲刺盾墙破风；弹幕反弹如雨，末端盾击强击退+中震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_BURST_II</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进 II·装</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>举盾冲刺，撞开路径敌人并反弹沿途弹幕</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>22+17</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>中距盾冲，冲刺中正面弹幕全部反弹；末端盾击击退</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 冲刺反弹 · 击退（防御向，伤害低于同档输出型）</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>冲刺盾墙破风；弹幕反弹如雨，末端盾击强击退+中震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_BURST_III</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进 III·装</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>举盾冲刺，撞开路径敌人并反弹沿途弹幕</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>25+20</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>中距盾冲，冲刺中正面弹幕全部反弹；末端盾击击退</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 冲刺反弹 · 击退（防御向，伤害低于同档输出型）</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>冲刺盾墙破风；弹幕反弹如雨，末端盾击强击退+中震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_BURST_I</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩 I·装</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>短蓄后破势冲锋，末端重斩</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>16+24</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>蓄力 0.6s 后向前冲锋，路径命中 + 末端重斩；对护盾/韧段伤害 +50%（破势）</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 蓄力冲锋 · 破势（对韧段加伤）</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>蓄力后爆发冲锋；破防瞬间碎甲迸溅+重震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_BURST_II</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩 II·装</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>短蓄后破势冲锋，末端重斩</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>19+29</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>蓄力 0.6s 后向前冲锋，路径命中 + 末端重斩；对护盾/韧段伤害 +50%（破势）</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 蓄力冲锋 · 破势（对韧段加伤）</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>蓄力后爆发冲锋；破防瞬间碎甲迸溅+重震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_BURST_III</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩 III·装</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>短蓄后破势冲锋，末端重斩</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>22+34</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>蓄力 0.6s 后向前冲锋，路径命中 + 末端重斩；对护盾/韧段伤害 +50%（破势）</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 蓄力冲锋 · 破势（对韧段加伤）</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>蓄力后爆发冲锋；破防瞬间碎甲迸溅+重震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_BURST_I</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺 I·装</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心向四周快速环形突刺</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>7×6</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心向 8 方向快速突刺 6 段，可边突边小幅位移；同一目标每段独立判定</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 环形突刺 · 多方向覆盖</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>八方刺影环绕；环形金属风暴，每段轻顿帧叠加成密集节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_BURST_II</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺 II·装</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心向四周快速环形突刺</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>8×6</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心向 8 方向快速突刺 6 段，可边突边小幅位移；同一目标每段独立判定</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 环形突刺 · 多方向覆盖</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>八方刺影环绕；环形金属风暴，每段轻顿帧叠加成密集节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_BURST_III</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺 III·装</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心向四周快速环形突刺</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>10×6</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心向 8 方向快速突刺 6 段，可边突边小幅位移；同一目标每段独立判定</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 环形突刺 · 多方向覆盖</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>八方刺影环绕；环形金属风暴，每段轻顿帧叠加成密集节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_BURST_I</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装 I·装</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>蓄势后一记砸穿，对破防敌人特攻</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>25+30</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>蓄势 0.8s 后一记砸穿；对处于破防窗口的敌人伤害 ×1.5</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 蓄势砸穿 · 破防特攻</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>蓄势重压画面下沉；砸穿破防瞬间碎甲爆裂+重震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_BURST_II</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装 II·装</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>蓄势后一记砸穿，对破防敌人特攻</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>30+36</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>蓄势 0.8s 后一记砸穿；对处于破防窗口的敌人伤害 ×1.5</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 蓄势砸穿 · 破防特攻</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>蓄势重压画面下沉；砸穿破防瞬间碎甲爆裂+重震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_BURST_III</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装 III·装</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>蓄势后一记砸穿，对破防敌人特攻</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>35+42</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>蓄势 0.8s 后一记砸穿；对处于破防窗口的敌人伤害 ×1.5</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 蓄势砸穿 · 破防特攻</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>蓄势重压画面下沉；砸穿破防瞬间碎甲爆裂+重震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_BURST_I</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击 I·装</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>突进斩，对已标记敌人伤害大幅提升</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>20+22</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>中距突进斩；命中已标记敌人时本次伤害 +60%，标记保留</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>无（不施加、不引爆标记）</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 突进 · 对标记敌加伤</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>突进斩击拖出裂纹光；标记爆闪+强顿帧</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_BURST_II</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击 II·装</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>突进斩，对已标记敌人伤害大幅提升</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>24+26</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>中距突进斩；命中已标记敌人时本次伤害 +60%，标记保留</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>无（不施加、不引爆标记）</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 突进 · 对标记敌加伤</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>突进斩击拖出裂纹光；标记爆闪+强顿帧</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_BURST_III</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击 III·装</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>突进斩，对已标记敌人伤害大幅提升</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>28+31</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>6s</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>中距突进斩；命中已标记敌人时本次伤害 +60%，标记保留</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>无（不施加、不引爆标记）</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 突进 · 对标记敌加伤</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>突进斩击拖出裂纹光；标记爆闪+强顿帧</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4093,7 +8641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5220,6 +9768,1626 @@
       <c r="L20" s="5" t="inlineStr">
         <is>
           <t>6 台齐轰弹幕倾泻，攻速buff时弹道撕空轰鸣；3s 后全体晶簇碎裂收束</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺 I·超</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>展开全域电场罩，罩内敌人迟滞，罩顶持续落雷</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>8×5</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心展开半径约 8m 的电场罩，持续 3s；罩内敌人移速 -40%、攻速 -20%；每 0.6s 落雷一次，共 5 次</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>每波落雷累计中等感电值</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 全域减速罩 · 降伤换功能（伤害明显低于同档超限）</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>罩体展开低频嗡鸣；落雷劈下白紫闪光+短震屏，罩内敌人动作迟滞、电弧缠身</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺 II·超</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>展开全域电场罩，罩内敌人迟滞，罩顶持续落雷</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>9×5</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心展开半径约 8m 的电场罩，持续 3s；罩内敌人移速 -40%、攻速 -20%；每 0.6s 落雷一次，共 5 次</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>每波落雷累计中等感电值</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 全域减速罩 · 降伤换功能（伤害明显低于同档超限）</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>罩体展开低频嗡鸣；落雷劈下白紫闪光+短震屏，罩内敌人动作迟滞、电弧缠身</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>BT_BOLT_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>雷矢链刺 III·超</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>展开全域电场罩，罩内敌人迟滞，罩顶持续落雷</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>11×5</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心展开半径约 8m 的电场罩，持续 3s；罩内敌人移速 -40%、攻速 -20%；每 0.6s 落雷一次，共 5 次</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>每波落雷累计中等感电值</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 全域减速罩 · 降伤换功能（伤害明显低于同档超限）</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>罩体展开低频嗡鸣；落雷劈下白紫闪光+短震屏，罩内敌人动作迟滞、电弧缠身</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃 I·超</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心爆发腐蚀领域，全场敌人被酸雾笼罩</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>8×5</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心展开半径约 9m 的腐蚀领域，持续 4s；每 0.8s 结算一次，共 5 次；领域内敌人移速 -35%</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>每波累计较高侵蚀值</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 全域侵蚀铺设 · 领域持续</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>酸雾海从脚下炸开并蔓延；群怪脚步迟滞、护甲冒烟，末波领域收缩爆散</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃 II·超</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心爆发腐蚀领域，全场敌人被酸雾笼罩</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>10×5</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心展开半径约 9m 的腐蚀领域，持续 4s；每 0.8s 结算一次，共 5 次；领域内敌人移速 -35%</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>每波累计较高侵蚀值</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 全域侵蚀铺设 · 领域持续</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>酸雾海从脚下炸开并蔓延；群怪脚步迟滞、护甲冒烟，末波领域收缩爆散</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLAW_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>侵蚀爪刃 III·超</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心爆发腐蚀领域，全场敌人被酸雾笼罩</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>12×5</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>以自身为中心展开半径约 9m 的腐蚀领域，持续 4s；每 0.8s 结算一次，共 5 次；领域内敌人移速 -35%</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>每波累计较高侵蚀值</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 全域侵蚀铺设 · 领域持续</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>酸雾海从脚下炸开并蔓延；群怪脚步迟滞、护甲冒烟，末波领域收缩爆散</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击 I·超</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>同时射出六根锚链锁定四周敌人，尽数拽向中心后乱刺</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>6+8+10+12+14</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>向四周射出 6 根锚链，将命中敌人拽向中心；随后 5 段乱刺，中心敌人受全额、外圈受 60%</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>无（控制类，非状态）</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 多钩卷怪 · 强聚怪控制（伤害低于同档输出型超限）</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>六链齐发破空声；群怪被拽向中心挤压碰撞，乱刺金属风暴+最大震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击 II·超</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>同时射出六根锚链锁定四周敌人，尽数拽向中心后乱刺</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>7+9+12+14+17</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>向四周射出 6 根锚链，将命中敌人拽向中心；随后 5 段乱刺，中心敌人受全额、外圈受 60%</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>无（控制类，非状态）</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 多钩卷怪 · 强聚怪控制（伤害低于同档输出型超限）</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>六链齐发破空声；群怪被拽向中心挤压碰撞，乱刺金属风暴+最大震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>BT_ANCHOR_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>索锚打击 III·超</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>同时射出六根锚链锁定四周敌人，尽数拽向中心后乱刺</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>8+10+14+17+20</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>向四周射出 6 根锚链，将命中敌人拽向中心；随后 5 段乱刺，中心敌人受全额、外圈受 60%</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>无（控制类，非状态）</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 多钩卷怪 · 强聚怪控制（伤害低于同档输出型超限）</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>六链齐发破空声；群怪被拽向中心挤压碰撞，乱刺金属风暴+最大震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击 I·超</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>升空后连续三次坠地震击，每次重新升空</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>30+40+50</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>升空至高空，连续三次坠地（每次重新升空），落点可微调；每次落地全屏震击</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 三次高空坠震 · 全屏震击</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>三次升空坠落，震屏逐级递增；末次落地全屏尘爆+镜头重震</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击 II·超</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>升空后连续三次坠地震击，每次重新升空</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>36+48+60</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>升空至高空，连续三次坠地（每次重新升空），落点可微调；每次落地全屏震击</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 三次高空坠震 · 全屏震击</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>三次升空坠落，震屏逐级递增；末次落地全屏尘爆+镜头重震</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>BT_QUAKE_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>爆震跃击 III·超</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>升空后连续三次坠地震击，每次重新升空</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>42+56+70</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>升空至高空，连续三次坠地（每次重新升空），落点可微调；每次落地全屏震击</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 三次高空坠震 · 全屏震击</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>三次升空坠落，震屏逐级递增；末次落地全屏尘爆+镜头重震</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进 I·超</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>展开减速护罩，罩内敌人迟滞，自身承伤降低</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>8+10+12+14</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>展开半径护罩 4s：罩内敌人移速 -40%；自身受到伤害 -50%；每 1s 罩缘冲击一次（共 4 次）</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 减速护罩 · 自身减伤（防御向超限，伤害最低档）</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>护罩展开低频嗡鸣；受击时护罩波纹扩散，罩内敌人动作迟滞</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进 II·超</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>展开减速护罩，罩内敌人迟滞，自身承伤降低</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>10+12+14+17</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>展开半径护罩 4s：罩内敌人移速 -40%；自身受到伤害 -50%；每 1s 罩缘冲击一次（共 4 次）</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 减速护罩 · 自身减伤（防御向超限，伤害最低档）</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>护罩展开低频嗡鸣；受击时护罩波纹扩散，罩内敌人动作迟滞</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>BT_BULWARK_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>筑垒推进 III·超</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>展开减速护罩，罩内敌人迟滞，自身承伤降低</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>12+14+17+20</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 75</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>展开半径护罩 4s：罩内敌人移速 -40%；自身受到伤害 -50%；每 1s 罩缘冲击一次（共 4 次）</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 减速护罩 · 自身减伤（防御向超限，伤害最低档）</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>护罩展开低频嗡鸣；受击时护罩波纹扩散，罩内敌人动作迟滞</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩 I·超</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>超长蓄力后释放一记贯穿前方的巨型斩</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>30+45+60</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 80</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>蓄力 2s（可移动微调，移速 -40%），释放贯穿前方长距的巨型斩；蓄力期间受击不打断但受伤 +20%</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 超长蓄力 · 巨型贯穿斩（高代价高单体）</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>2s 蓄力张力拉满、画面暗角收缩；释放全屏横斩+最大震屏，地面留下长距刀痕</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩 II·超</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>超长蓄力后释放一记贯穿前方的巨型斩</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>36+54+72</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 80</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>蓄力 2s（可移动微调，移速 -40%），释放贯穿前方长距的巨型斩；蓄力期间受击不打断但受伤 +20%</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 超长蓄力 · 巨型贯穿斩（高代价高单体）</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>2s 蓄力张力拉满、画面暗角收缩；释放全屏横斩+最大震屏，地面留下长距刀痕</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>BT_CLEAVE_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>蓄力重斩 III·超</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>超长蓄力后释放一记贯穿前方的巨型斩</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>42+63+84</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 80</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>蓄力 2s（可移动微调，移速 -40%），释放贯穿前方长距的巨型斩；蓄力期间受击不打断但受伤 +20%</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 超长蓄力 · 巨型贯穿斩（高代价高单体）</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>2s 蓄力张力拉满、画面暗角收缩；释放全屏横斩+最大震屏，地面留下长距刀痕</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺 I·超</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>2.5 秒内高频乱刺，专攻韧段</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>5×10</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>2.5s 内高频乱刺 10 段，每段附高削韧量；可边刺边小幅位移</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 高频乱刺 · 高削韧（破韧向超限）</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>暴风骤雨刺击；韧段碎裂声连成一片，末段韧段崩塌大震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺 II·超</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>2.5 秒内高频乱刺，专攻韧段</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>6×10</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>2.5s 内高频乱刺 10 段，每段附高削韧量；可边刺边小幅位移</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 高频乱刺 · 高削韧（破韧向超限）</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>暴风骤雨刺击；韧段碎裂声连成一片，末段韧段崩塌大震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>BT_THRUST_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>多重连刺 III·超</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>2.5 秒内高频乱刺，专攻韧段</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>7×10</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>2.5s 内高频乱刺 10 段，每段附高削韧量；可边刺边小幅位移</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 高频乱刺 · 高削韧（破韧向超限）</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>暴风骤雨刺击；韧段碎裂声连成一片，末段韧段崩塌大震屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装 I·超</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>连续四次大范围砸地，逐次加重</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>20+25+30+35</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>连续四次大范围砸地，每次命中大幅削韧；对破防敌人额外 +30%</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 四连砸 · 削韧破防</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>四次砸地逐级加重，震屏层层叠加；末次破防碎裂全屏白光</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装 II·超</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>连续四次大范围砸地，逐次加重</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>24+30+36+42</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>连续四次大范围砸地，每次命中大幅削韧；对破防敌人额外 +30%</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 四连砸 · 削韧破防</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>四次砸地逐级加重，震屏层层叠加；末次破防碎裂全屏白光</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>BT_BREAKER_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>破韧重装 III·超</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>连续四次大范围砸地，逐次加重</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>28+35+42+49</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>连续四次大范围砸地，每次命中大幅削韧；对破防敌人额外 +30%</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 四连砸 · 削韧破防</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>四次砸地逐级加重，震屏层层叠加；末次破防碎裂全屏白光</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_DRAGON_I</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击 I·超</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>瞬移至每个已标记敌人身边各斩一刀</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>每个 22（上限 6 个）</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>瞬移至每个已标记敌人身边各斩一刀（上限 6 个），不引爆标记</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>无（不施加、不引爆标记）</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 多目标标记连锁 · 不引爆（标记联动向超限）</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>连锁瞬移斩，标记逐个爆闪；末次收刀全屏裂纹光收束</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_DRAGON_II</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击 II·超</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>瞬移至每个已标记敌人身边各斩一刀</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>每个 26（上限 6 个）</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>瞬移至每个已标记敌人身边各斩一刀（上限 6 个），不引爆标记</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>无（不施加、不引爆标记）</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 多目标标记连锁 · 不引爆（标记联动向超限）</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>连锁瞬移斩，标记逐个爆闪；末次收刀全屏裂纹光收束</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>BT_SCAR_DRAGON_III</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>铭痕裂击 III·超</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>瞬移至每个已标记敌人身边各斩一刀</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>每个 31（上限 6 个）</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>热能 ≥ 70</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>瞬移至每个已标记敌人身边各斩一刀（上限 6 个），不引爆标记</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>无（不施加、不引爆标记）</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>近战 · 多目标标记连锁 · 不引爆（标记联动向超限）</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>连锁瞬移斩，标记逐个爆闪；末次收刀全屏裂纹光收束</t>
         </is>
       </c>
     </row>
@@ -5296,7 +11464,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>行为插件（命中累计状态值，满条施加而非必中）</t>
+          <t>行为插件（命中累计状态值，满条施加而非必中）；标记例外：施加 / 引爆走赋能，行为插件只做「命中已标记敌人」联动</t>
         </is>
       </c>
     </row>
@@ -5325,7 +11493,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>范围 / 弹道 / 追踪 / 多重 / 环绕 / 触达</t>
+          <t>范围 / 弹道 / 追踪 / 多重 / 环绕 / 公转 / 触达 / 散射</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -5342,7 +11510,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>事件型：击中 / 累积 / 计时；状态型：命中燃烧 / 感电 / 侵蚀 / 失衡 / 标记</t>
+          <t>事件型：击中 / 累积 / 计时 / 召唤物销毁 / 命中暴击；状态型：命中燃烧 / 感电 / 失衡</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
